--- a/data/datasets/separable/separable_test.xlsx
+++ b/data/datasets/separable/separable_test.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R374e9820778e4f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcdd5c3915f8a48de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -495,10 +495,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>y^{\prime}=- e^{- x} \operatorname{ctan}{\left(x \right)} \log{\left(e \right)} + e^{- x} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
+        <x:v>y^{\prime}=- \frac{e^{x} \left(- 2 \tan^{2}{\left(2 x \right)} - 2\right)}{\tan^{2}{\left(2 x \right)}} - \frac{e^{x} \log{\left(e \right)}}{\tan{\left(2 x \right)}} - \frac{2 \operatorname{acos}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{atan}{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>y=\ctg(x) \cdot \frac{1}{e^{x}}+\arcctg(2 \cdot x) \cdot \arcctg(x)+C</x:v>
+        <x:v>y=\arccos(x) \cdot \frac{1}{\arctg(2 \cdot x)}-e^{x} \cdot \frac{1}{\tg(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>separable variables</x:v>
@@ -506,10 +506,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>y^{\prime}=- \frac{e^{x} \left(- 2 \tan^{2}{\left(2 x \right)} - 2\right)}{\tan^{2}{\left(2 x \right)}} - \frac{e^{x} \log{\left(e \right)}}{\tan{\left(2 x \right)}} - \frac{2 \operatorname{acos}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{atan}{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=\sin{\left(x \right)} \operatorname{acos}{\left(x \right)} - \sin{\left(x \right)} \operatorname{asin}{\left(x \right)} + \frac{2 \cos{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>y=\arccos(x) \cdot \frac{1}{\arctg(2 \cdot x)}-e^{x} \cdot \frac{1}{\tg(2 \cdot x)}+C</x:v>
+        <x:v>y=\cos(x) \cdot \arcsin(x)-\arccos(x) \cdot \cos(x)+C</x:v>
       </x:c>
       <x:c r="C10" t="str">
         <x:v>separable variables</x:v>
@@ -517,10 +517,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>y^{\prime}=\sin{\left(x \right)} \operatorname{acos}{\left(x \right)} - \sin{\left(x \right)} \operatorname{asin}{\left(x \right)} + \frac{2 \cos{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
+        <x:v>y^{\prime}=- \frac{x^{2}}{\sqrt{1 - x^{2}}} - 2 x \operatorname{asin}{\left(x \right)} - \operatorname{ctan}{\left(2 x \right)} \sin{\left(x \right)} + 2 \cos{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>y=\cos(x) \cdot \arcsin(x)-\arccos(x) \cdot \cos(x)+C</x:v>
+        <x:v>y=\cos(x) \cdot \ctg(2 \cdot x)-x^{2} \cdot \arcsin(x)+C</x:v>
       </x:c>
       <x:c r="C11" t="str">
         <x:v>separable variables</x:v>
@@ -528,10 +528,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>y^{\prime}=- \frac{x^{2}}{\sqrt{1 - x^{2}}} - 2 x \operatorname{asin}{\left(x \right)} - \operatorname{ctan}{\left(2 x \right)} \sin{\left(x \right)} + 2 \cos{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}</x:v>
+        <x:v>y^{\prime}=x^{3} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + 3 x^{2} \operatorname{ctan}{\left(x \right)} + 2 e^{- 2 x} x^{2} \log{\left(e \right)} - 2 e^{- 2 x} x</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>y=\cos(x) \cdot \ctg(2 \cdot x)-x^{2} \cdot \arcsin(x)+C</x:v>
+        <x:v>y=\ctg(x) \cdot x^{3}-x^{2} \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
       <x:c r="C12" t="str">
         <x:v>separable variables</x:v>
@@ -539,10 +539,10 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>y^{\prime}=x^{3} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + 3 x^{2} \operatorname{ctan}{\left(x \right)} + 2 e^{- 2 x} x^{2} \log{\left(e \right)} - 2 e^{- 2 x} x</x:v>
+        <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \log{\left(x \right)} + \frac{e^{2 x}}{x} + \frac{2 \operatorname{acos}{\left(2 x \right)}}{4 x^{2} + 1} - \frac{2 \operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>y=\ctg(x) \cdot x^{3}-x^{2} \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
+        <x:v>y=\arccos(2 \cdot x) \cdot \arctg(2 \cdot x)+e^{2 \cdot x} \cdot \ln(x)+C</x:v>
       </x:c>
       <x:c r="C13" t="str">
         <x:v>separable variables</x:v>
@@ -550,10 +550,10 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \log{\left(x \right)} + \frac{e^{2 x}}{x} + \frac{2 \operatorname{acos}{\left(2 x \right)}}{4 x^{2} + 1} - \frac{2 \operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
+        <x:v>y^{\prime}=\frac{2 \operatorname{asin}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{acot}^{2}{\left(2 x \right)}} + \frac{1}{\sqrt{1 - x^{2}} \operatorname{acot}{\left(2 x \right)}} - \frac{2 \operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>y=\arccos(2 \cdot x) \cdot \arctg(2 \cdot x)+e^{2 \cdot x} \cdot \ln(x)+C</x:v>
+        <x:v>y=\arcsin(x) \cdot \frac{1}{\arcctg(2 \cdot x)}+\arccos(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C14" t="str">
         <x:v>separable variables</x:v>
@@ -561,10 +561,10 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>y^{\prime}=\frac{2 \operatorname{asin}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{acot}^{2}{\left(2 x \right)}} + \frac{1}{\sqrt{1 - x^{2}} \operatorname{acot}{\left(2 x \right)}} - \frac{2 \operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=\frac{\cos{\left(x \right)}}{\operatorname{atan}{\left(2 x \right)}} - \frac{2 \sin{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{2 \operatorname{asin}{\left(2 x \right)}}{4 x^{2} + 1} + \frac{2 \operatorname{acot}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>y=\arcsin(x) \cdot \frac{1}{\arcctg(2 \cdot x)}+\arccos(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
+        <x:v>y=\arcsin(2 \cdot x) \cdot \arcctg(2 \cdot x)+\sin(x) \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C15" t="str">
         <x:v>separable variables</x:v>
@@ -572,10 +572,10 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>y^{\prime}=\frac{\cos{\left(x \right)}}{\operatorname{atan}{\left(2 x \right)}} - \frac{2 \sin{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{2 \operatorname{asin}{\left(2 x \right)}}{4 x^{2} + 1} + \frac{2 \operatorname{acot}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
+        <x:v>y^{\prime}=x \left(\tan^{2}{\left(x \right)} + 1\right) - 2 \sin{\left(2 x \right)} \operatorname{acos}{\left(x \right)} + \tan{\left(x \right)} - \frac{\cos{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>y=\arcsin(2 \cdot x) \cdot \arcctg(2 \cdot x)+\sin(x) \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
+        <x:v>y=\cos(2 \cdot x) \cdot \arccos(x)+x \cdot \tg(x)+C</x:v>
       </x:c>
       <x:c r="C16" t="str">
         <x:v>separable variables</x:v>
@@ -583,10 +583,10 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>y^{\prime}=x \left(\tan^{2}{\left(x \right)} + 1\right) - 2 \sin{\left(2 x \right)} \operatorname{acos}{\left(x \right)} + \tan{\left(x \right)} - \frac{\cos{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
+        <x:v>y^{\prime}=x^{3} \left(2 \tan^{2}{\left(2 x \right)} + 2\right) + 3 x^{2} \tan{\left(2 x \right)} - 2 e^{- 2 x} \log{\left(e \right)} \operatorname{acos}{\left(x \right)} - \frac{e^{- 2 x}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>y=\cos(2 \cdot x) \cdot \arccos(x)+x \cdot \tg(x)+C</x:v>
+        <x:v>y=\tg(2 \cdot x) \cdot x^{3}+\arccos(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
       <x:c r="C17" t="str">
         <x:v>separable variables</x:v>
@@ -594,10 +594,10 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>y^{\prime}=x^{3} \left(2 \tan^{2}{\left(2 x \right)} + 2\right) + 3 x^{2} \tan{\left(2 x \right)} - 2 e^{- 2 x} \log{\left(e \right)} \operatorname{acos}{\left(x \right)} - \frac{e^{- 2 x}}{\sqrt{1 - x^{2}}}</x:v>
+        <x:v>y^{\prime}=\frac{e^{x} \log{\left(e \right)}}{\operatorname{atan}{\left(2 x \right)}} - \frac{2 e^{x}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{\log{\left(x \right)}}{\sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{x}</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>y=\tg(2 \cdot x) \cdot x^{3}+\arccos(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
+        <x:v>y=\ln(x) \cdot \arccos(x)+e^{x} \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C18" t="str">
         <x:v>separable variables</x:v>
@@ -605,10 +605,10 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>y^{\prime}=\frac{e^{x} \log{\left(e \right)}}{\operatorname{atan}{\left(2 x \right)}} - \frac{2 e^{x}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{\log{\left(x \right)}}{\sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{x}</x:v>
+        <x:v>y^{\prime}=-2 - \frac{2 \cos^{2}{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} - 2 e^{- 2 x} \log{\left(e \right)} \sin{\left(x \right)} + e^{- 2 x} \cos{\left(x \right)}</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>y=\ln(x) \cdot \arccos(x)+e^{x} \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
+        <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\sin(2 \cdot x)}+\sin(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
       <x:c r="C19" t="str">
         <x:v>separable variables</x:v>
@@ -616,10 +616,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>y^{\prime}=-2 - \frac{2 \cos^{2}{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} - 2 e^{- 2 x} \log{\left(e \right)} \sin{\left(x \right)} + e^{- 2 x} \cos{\left(x \right)}</x:v>
+        <x:v>y^{\prime}=x^{3} \sin{\left(x \right)} - 3 x^{2} \cos{\left(x \right)} + 2 x^{2} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + 2 x \operatorname{ctan}{\left(2 x \right)}</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\sin(2 \cdot x)}+\sin(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
+        <x:v>y=\ctg(2 \cdot x) \cdot x^{2}-\cos(x) \cdot x^{3}+C</x:v>
       </x:c>
       <x:c r="C20" t="str">
         <x:v>separable variables</x:v>
@@ -627,10 +627,10 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>y^{\prime}=x^{3} \sin{\left(x \right)} - 3 x^{2} \cos{\left(x \right)} + 2 x^{2} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + 2 x \operatorname{ctan}{\left(2 x \right)}</x:v>
+        <x:v>y^{\prime}=2 x^{2} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + 2 x \operatorname{ctan}{\left(2 x \right)} + \frac{2 \cos{\left(2 x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>y=\ctg(2 \cdot x) \cdot x^{2}-\cos(x) \cdot x^{3}+C</x:v>
+        <x:v>y=\ctg(2 \cdot x) \cdot x^{2}+\sin(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C21" t="str">
         <x:v>separable variables</x:v>
@@ -638,10 +638,10 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>y^{\prime}=2 x^{2} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + 2 x \operatorname{ctan}{\left(2 x \right)} + \frac{2 \cos{\left(2 x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=2 x \log{\left(x \right)} + x + \frac{\tan^{2}{\left(x \right)} + 1}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \tan{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>y=\ctg(2 \cdot x) \cdot x^{2}+\sin(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
+        <x:v>y=x^{2} \cdot \ln(x)+\tg(x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C22" t="str">
         <x:v>separable variables</x:v>
@@ -649,10 +649,10 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>y^{\prime}=2 x \log{\left(x \right)} + x + \frac{\tan^{2}{\left(x \right)} + 1}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \tan{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=\frac{2 \sin{\left(2 x \right)} \operatorname{acot}{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \cos{\left(2 x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{asin}{\left(2 x \right)}} - \frac{2 \operatorname{acot}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>y=x^{2} \cdot \ln(x)+\tg(x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
+        <x:v>y=\arcctg(x) \cdot \frac{1}{\arcsin(2 \cdot x)}+\arcctg(2 \cdot x) \cdot \frac{1}{\cos(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C23" t="str">
         <x:v>separable variables</x:v>
@@ -660,10 +660,10 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>y^{\prime}=\frac{2 \sin{\left(2 x \right)} \operatorname{acot}{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \cos{\left(2 x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{asin}{\left(2 x \right)}} - \frac{2 \operatorname{acot}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=- 2 \sin{\left(2 x \right)} \operatorname{asin}{\left(x \right)} + \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{atan}{\left(x \right)}} - \frac{\operatorname{ctan}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} + \frac{\cos{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>y=\arcctg(x) \cdot \frac{1}{\arcsin(2 \cdot x)}+\arcctg(2 \cdot x) \cdot \frac{1}{\cos(2 \cdot x)}+C</x:v>
+        <x:v>y=\arcsin(x) \cdot \cos(2 \cdot x)+\ctg(x) \cdot \frac{1}{\arctg(x)}+C</x:v>
       </x:c>
       <x:c r="C24" t="str">
         <x:v>separable variables</x:v>
@@ -671,10 +671,10 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>y^{\prime}=- 2 \sin{\left(2 x \right)} \operatorname{asin}{\left(x \right)} + \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{atan}{\left(x \right)}} - \frac{\operatorname{ctan}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} + \frac{\cos{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
+        <x:v>y^{\prime}=\frac{2 \operatorname{atan}{\left(x \right)}}{4 x^{2} + 1} + \frac{\operatorname{atan}{\left(2 x \right)}}{x^{2} + 1} - 2 e^{- 2 x} x^{2} \log{\left(e \right)} + 2 e^{- 2 x} x</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>y=\arcsin(x) \cdot \cos(2 \cdot x)+\ctg(x) \cdot \frac{1}{\arctg(x)}+C</x:v>
+        <x:v>y=\arctg(x) \cdot \arctg(2 \cdot x)+x^{2} \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
       <x:c r="C25" t="str">
         <x:v>separable variables</x:v>
@@ -682,10 +682,10 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>y^{\prime}=\frac{2 \operatorname{atan}{\left(x \right)}}{4 x^{2} + 1} + \frac{\operatorname{atan}{\left(2 x \right)}}{x^{2} + 1} - 2 e^{- 2 x} x^{2} \log{\left(e \right)} + 2 e^{- 2 x} x</x:v>
+        <x:v>y^{\prime}=- \frac{x \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{1}{\sin{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>y=\arctg(x) \cdot \arctg(2 \cdot x)+x^{2} \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
+        <x:v>y=x \cdot \frac{1}{\sin(x)}-\arctg(x) \cdot \sin(2 \cdot x)+C</x:v>
       </x:c>
       <x:c r="C26" t="str">
         <x:v>separable variables</x:v>
@@ -693,10 +693,10 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>y^{\prime}=- \frac{x \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{1}{\sin{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=- \frac{x^{2}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} + \frac{2 x}{\operatorname{atan}{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>y=x \cdot \frac{1}{\sin(x)}-\arctg(x) \cdot \sin(2 \cdot x)+C</x:v>
+        <x:v>y=x^{2} \cdot \frac{1}{\arctg(x)}+\tg(2 \cdot x) \cdot \ln(x)+C</x:v>
       </x:c>
       <x:c r="C27" t="str">
         <x:v>separable variables</x:v>
@@ -704,10 +704,10 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>y^{\prime}=- \frac{x^{2}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} + \frac{2 x}{\operatorname{atan}{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=\frac{\left(- \tan^{2}{\left(x \right)} - 1\right) \cos{\left(x \right)}}{\tan^{2}{\left(x \right)}} - \frac{\sin{\left(x \right)}}{\tan{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>y=x^{2} \cdot \frac{1}{\arctg(x)}+\tg(2 \cdot x) \cdot \ln(x)+C</x:v>
+        <x:v>y=\cos(x) \cdot \frac{1}{\tg(x)}-\ln(2 \cdot x) \cdot \arctg(x)+C</x:v>
       </x:c>
       <x:c r="C28" t="str">
         <x:v>separable variables</x:v>
@@ -715,10 +715,10 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>y^{\prime}=\frac{\left(- \tan^{2}{\left(x \right)} - 1\right) \cos{\left(x \right)}}{\tan^{2}{\left(x \right)}} - \frac{\sin{\left(x \right)}}{\tan{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=- \frac{2 x^{3} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} + \frac{3 x^{2}}{\operatorname{ctan}{\left(2 x \right)}} + \frac{\operatorname{acos}{\left(2 x \right)}}{x^{2} + 1} - \frac{2 \operatorname{atan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>y=\cos(x) \cdot \frac{1}{\tg(x)}-\ln(2 \cdot x) \cdot \arctg(x)+C</x:v>
+        <x:v>y=\arccos(2 \cdot x) \cdot \arctg(x)+x^{3} \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C29" t="str">
         <x:v>separable variables</x:v>
@@ -726,10 +726,10 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>y^{\prime}=- \frac{2 x^{3} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} + \frac{3 x^{2}}{\operatorname{ctan}{\left(2 x \right)}} + \frac{\operatorname{acos}{\left(2 x \right)}}{x^{2} + 1} - \frac{2 \operatorname{atan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
+        <x:v>y^{\prime}=\frac{2 \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\log{\left(2 x \right)}} - \frac{\operatorname{ctan}{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>y=\arccos(2 \cdot x) \cdot \arctg(x)+x^{3} \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
+        <x:v>y=\ctg(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}-x \cdot \arcctg(x)+C</x:v>
       </x:c>
       <x:c r="C30" t="str">
         <x:v>separable variables</x:v>
@@ -737,10 +737,10 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>y^{\prime}=\frac{2 \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\log{\left(2 x \right)}} - \frac{\operatorname{ctan}{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
+        <x:v>y^{\prime}=5 x^{4} + \frac{2 \operatorname{asin}{\left(2 x \right)}}{4 x^{2} + 1} + \frac{2 \operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>y=\ctg(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}-x \cdot \arcctg(x)+C</x:v>
+        <x:v>y=x^{3} \cdot x^{2}+\arctg(2 \cdot x) \cdot \arcsin(2 \cdot x)+C</x:v>
       </x:c>
       <x:c r="C31" t="str">
         <x:v>separable variables</x:v>
@@ -748,10 +748,10 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>y^{\prime}=5 x^{4} + \frac{2 \operatorname{asin}{\left(2 x \right)}}{4 x^{2} + 1} + \frac{2 \operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
+        <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \sin{\left(x \right)} + e^{2 x} \cos{\left(x \right)} + 2 \cos{\left(2 x \right)} \operatorname{asin}{\left(x \right)} + \frac{\sin{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>y=x^{3} \cdot x^{2}+\arctg(2 \cdot x) \cdot \arcsin(2 \cdot x)+C</x:v>
+        <x:v>y=e^{2 \cdot x} \cdot \sin(x)+\arcsin(x) \cdot \sin(2 \cdot x)+C</x:v>
       </x:c>
       <x:c r="C32" t="str">
         <x:v>separable variables</x:v>
@@ -759,10 +759,10 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \sin{\left(x \right)} + e^{2 x} \cos{\left(x \right)} + 2 \cos{\left(2 x \right)} \operatorname{asin}{\left(x \right)} + \frac{\sin{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
+        <x:v>y^{\prime}=e^{x} \left(\tan^{2}{\left(x \right)} + 1\right) + e^{x} \log{\left(e \right)} \tan{\left(x \right)} - \frac{\operatorname{acot}{\left(x \right)}}{x^{2} + 1} + \frac{\operatorname{atan}{\left(x \right)}}{x^{2} + 1}</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>y=e^{2 \cdot x} \cdot \sin(x)+\arcsin(x) \cdot \sin(2 \cdot x)+C</x:v>
+        <x:v>y=e^{x} \cdot \tg(x)-\arctg(x) \cdot \arcctg(x)+C</x:v>
       </x:c>
       <x:c r="C33" t="str">
         <x:v>separable variables</x:v>
@@ -770,10 +770,10 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>y^{\prime}=e^{x} \left(\tan^{2}{\left(x \right)} + 1\right) + e^{x} \log{\left(e \right)} \tan{\left(x \right)} - \frac{\operatorname{acot}{\left(x \right)}}{x^{2} + 1} + \frac{\operatorname{atan}{\left(x \right)}}{x^{2} + 1}</x:v>
+        <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{asin}{\left(x \right)} + \frac{\log{\left(x \right)}}{x^{2} + 1} + \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}} + \frac{\operatorname{atan}{\left(x \right)}}{x}</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>y=e^{x} \cdot \tg(x)-\arctg(x) \cdot \arcctg(x)+C</x:v>
+        <x:v>y=\tg(x) \cdot \arcsin(x)+\ln(x) \cdot \arctg(x)+C</x:v>
       </x:c>
       <x:c r="C34" t="str">
         <x:v>separable variables</x:v>
@@ -781,10 +781,10 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{asin}{\left(x \right)} + \frac{\log{\left(x \right)}}{x^{2} + 1} + \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}} + \frac{\operatorname{atan}{\left(x \right)}}{x}</x:v>
+        <x:v>y^{\prime}=\frac{x \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{x}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} + \frac{1}{\operatorname{asin}{\left(x \right)}} - \frac{1}{\operatorname{ctan}{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>y=\tg(x) \cdot \arcsin(x)+\ln(x) \cdot \arctg(x)+C</x:v>
+        <x:v>y=x \cdot \frac{1}{\arcsin(x)}-x \cdot \frac{1}{\ctg(x)}+C</x:v>
       </x:c>
       <x:c r="C35" t="str">
         <x:v>separable variables</x:v>
@@ -792,10 +792,10 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>y^{\prime}=\frac{x \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{x}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} + \frac{1}{\operatorname{asin}{\left(x \right)}} - \frac{1}{\operatorname{ctan}{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=\frac{x^{2}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}} + \frac{2 x}{\operatorname{acos}{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>y=x \cdot \frac{1}{\arcsin(x)}-x \cdot \frac{1}{\ctg(x)}+C</x:v>
+        <x:v>y=x^{2} \cdot \frac{1}{\arccos(x)}-\arcsin(2 \cdot x) \cdot \sin(x)+C</x:v>
       </x:c>
       <x:c r="C36" t="str">
         <x:v>separable variables</x:v>
@@ -803,10 +803,10 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>y^{\prime}=\frac{x^{2}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}} + \frac{2 x}{\operatorname{acos}{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=\frac{\sin^{2}{\left(x \right)}}{\cos^{2}{\left(x \right)}} + 1 + \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{x^{2}} - \frac{2 \operatorname{ctan}{\left(x \right)}}{x^{3}}</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>y=x^{2} \cdot \frac{1}{\arccos(x)}-\arcsin(2 \cdot x) \cdot \sin(x)+C</x:v>
+        <x:v>y=\sin(x) \cdot \frac{1}{\cos(x)}+\ctg(x) \cdot \frac{1}{x^{2}}+C</x:v>
       </x:c>
       <x:c r="C37" t="str">
         <x:v>separable variables</x:v>
@@ -814,10 +814,10 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
-        <x:v>y^{\prime}=\frac{\sin^{2}{\left(x \right)}}{\cos^{2}{\left(x \right)}} + 1 + \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{x^{2}} - \frac{2 \operatorname{ctan}{\left(x \right)}}{x^{3}}</x:v>
+        <x:v>y^{\prime}=- \frac{x^{2} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{2 x}{\sin{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>y=\sin(x) \cdot \frac{1}{\cos(x)}+\ctg(x) \cdot \frac{1}{x^{2}}+C</x:v>
+        <x:v>y=x^{2} \cdot \frac{1}{\sin(x)}-\arccos(x) \cdot \sin(x)+C</x:v>
       </x:c>
       <x:c r="C38" t="str">
         <x:v>separable variables</x:v>
@@ -825,10 +825,10 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
-        <x:v>y^{\prime}=- \frac{x^{2} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{2 x}{\sin{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=- \frac{2 \sin{\left(2 x \right)}}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \cos{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - 2 e^{- 2 x} x^{2} \log{\left(e \right)} + 2 e^{- 2 x} x</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>y=x^{2} \cdot \frac{1}{\sin(x)}-\arccos(x) \cdot \sin(x)+C</x:v>
+        <x:v>y=x^{2} \cdot \frac{1}{e^{2 \cdot x}}+\cos(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C39" t="str">
         <x:v>separable variables</x:v>
@@ -836,10 +836,10 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
-        <x:v>y^{\prime}=- \frac{2 \sin{\left(2 x \right)}}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \cos{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - 2 e^{- 2 x} x^{2} \log{\left(e \right)} + 2 e^{- 2 x} x</x:v>
+        <x:v>y^{\prime}=- 2 e^{- 2 x} \log{\left(e \right)} \sin{\left(2 x \right)} + 2 e^{- 2 x} \cos{\left(2 x \right)}</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>y=x^{2} \cdot \frac{1}{e^{2 \cdot x}}+\cos(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
+        <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{e^{2 \cdot x}}-\arctg(2 \cdot x) \cdot \ctg(x)+C</x:v>
       </x:c>
       <x:c r="C40" t="str">
         <x:v>separable variables</x:v>
@@ -847,10 +847,10 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
-        <x:v>y^{\prime}=- 2 e^{- 2 x} \log{\left(e \right)} \sin{\left(2 x \right)} + 2 e^{- 2 x} \cos{\left(2 x \right)}</x:v>
+        <x:v>y^{\prime}=\frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{x^{2}} - \frac{2 \operatorname{ctan}{\left(x \right)}}{x^{3}}</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{e^{2 \cdot x}}-\arctg(2 \cdot x) \cdot \ctg(x)+C</x:v>
+        <x:v>y=\ctg(x) \cdot \frac{1}{x^{2}}+e^{x} \cdot \arcctg(2 \cdot x)+C</x:v>
       </x:c>
       <x:c r="C41" t="str">
         <x:v>separable variables</x:v>
@@ -858,10 +858,10 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
-        <x:v>y^{\prime}=\frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{x^{2}} - \frac{2 \operatorname{ctan}{\left(x \right)}}{x^{3}}</x:v>
+        <x:v>y^{\prime}=- \frac{\tan^{2}{\left(x \right)} + 1}{\sin{\left(2 x \right)}} + \frac{\left(- 2 \tan^{2}{\left(2 x \right)} - 2\right) \sin{\left(2 x \right)}}{\tan^{2}{\left(2 x \right)}} + \frac{2 \cos{\left(2 x \right)}}{\tan{\left(2 x \right)}} + \frac{2 \cos{\left(2 x \right)} \tan{\left(x \right)}}{\sin^{2}{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B42" t="str">
-        <x:v>y=\ctg(x) \cdot \frac{1}{x^{2}}+e^{x} \cdot \arcctg(2 \cdot x)+C</x:v>
+        <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{\tg(2 \cdot x)}-\tg(x) \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C42" t="str">
         <x:v>separable variables</x:v>
@@ -869,10 +869,10 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
-        <x:v>y^{\prime}=- \frac{\tan^{2}{\left(x \right)} + 1}{\sin{\left(2 x \right)}} + \frac{\left(- 2 \tan^{2}{\left(2 x \right)} - 2\right) \sin{\left(2 x \right)}}{\tan^{2}{\left(2 x \right)}} + \frac{2 \cos{\left(2 x \right)}}{\tan{\left(2 x \right)}} + \frac{2 \cos{\left(2 x \right)} \tan{\left(x \right)}}{\sin^{2}{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=- \frac{\operatorname{asin}{\left(x \right)}}{x^{2} + 1} + \frac{\operatorname{acot}{\left(x \right)}}{\sqrt{1 - x^{2}}} + \frac{1}{x \sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{x^{2}}</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{\tg(2 \cdot x)}-\tg(x) \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
+        <x:v>y=\arcsin(x) \cdot \arcctg(x)-\arccos(x) \cdot \frac{1}{x}+C</x:v>
       </x:c>
       <x:c r="C43" t="str">
         <x:v>separable variables</x:v>
@@ -880,10 +880,10 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
-        <x:v>y^{\prime}=- \frac{\operatorname{asin}{\left(x \right)}}{x^{2} + 1} + \frac{\operatorname{acot}{\left(x \right)}}{\sqrt{1 - x^{2}}} + \frac{1}{x \sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{x^{2}}</x:v>
+        <x:v>y^{\prime}=- \frac{2 \operatorname{atan}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} + \frac{2}{\left(4 x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}} + \frac{2 \operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} - \frac{2 \operatorname{asin}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>y=\arcsin(x) \cdot \arcctg(x)-\arccos(x) \cdot \frac{1}{x}+C</x:v>
+        <x:v>y=\arcsin(2 \cdot x) \cdot \arccos(2 \cdot x)+\arctg(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C44" t="str">
         <x:v>separable variables</x:v>
@@ -891,10 +891,10 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
-        <x:v>y^{\prime}=- \frac{2 \operatorname{atan}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} + \frac{2}{\left(4 x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}} + \frac{2 \operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} - \frac{2 \operatorname{asin}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
+        <x:v>y^{\prime}=- \frac{\sin{\left(x \right)}}{\operatorname{acos}{\left(2 x \right)}} + \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>y=\arcsin(2 \cdot x) \cdot \arccos(2 \cdot x)+\arctg(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
+        <x:v>y=\cos(x) \cdot \frac{1}{\arccos(2 \cdot x)}-\ctg(2 \cdot x) \cdot \arccos(2 \cdot x)+C</x:v>
       </x:c>
       <x:c r="C45" t="str">
         <x:v>separable variables</x:v>
@@ -902,10 +902,10 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
-        <x:v>y^{\prime}=- \frac{\sin{\left(x \right)}}{\operatorname{acos}{\left(2 x \right)}} + \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=- 2 x^{2} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - 2 x \operatorname{ctan}{\left(2 x \right)} + \frac{\operatorname{acos}{\left(x \right)}}{\sqrt{1 - x^{2}}} - \frac{\operatorname{asin}{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>y=\cos(x) \cdot \frac{1}{\arccos(2 \cdot x)}-\ctg(2 \cdot x) \cdot \arccos(2 \cdot x)+C</x:v>
+        <x:v>y=\arcsin(x) \cdot \arccos(x)-x^{2} \cdot \ctg(2 \cdot x)+C</x:v>
       </x:c>
       <x:c r="C46" t="str">
         <x:v>separable variables</x:v>
@@ -913,10 +913,10 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
-        <x:v>y^{\prime}=- 2 x^{2} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - 2 x \operatorname{ctan}{\left(2 x \right)} + \frac{\operatorname{acos}{\left(x \right)}}{\sqrt{1 - x^{2}}} - \frac{\operatorname{asin}{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
+        <x:v>y^{\prime}=- \frac{\sin{\left(x \right)}}{\operatorname{atan}{\left(2 x \right)}} - \frac{2 \cos{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B47" t="str">
-        <x:v>y=\arcsin(x) \cdot \arccos(x)-x^{2} \cdot \ctg(2 \cdot x)+C</x:v>
+        <x:v>y=\cos(x) \cdot \frac{1}{\arctg(2 \cdot x)}+\tg(x) \cdot \ln(x)+C</x:v>
       </x:c>
       <x:c r="C47" t="str">
         <x:v>separable variables</x:v>
@@ -924,10 +924,10 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
-        <x:v>y^{\prime}=- \frac{\sin{\left(x \right)}}{\operatorname{atan}{\left(2 x \right)}} - \frac{2 \cos{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=\frac{x^{2}}{\left(x^{2} + 1\right) \operatorname{acot}^{2}{\left(x \right)}} + \frac{2 x}{\operatorname{acot}{\left(x \right)}} + \frac{1}{\left(x^{2} + 1\right) \operatorname{asin}{\left(x \right)}} - \frac{\operatorname{atan}{\left(x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>y=\cos(x) \cdot \frac{1}{\arctg(2 \cdot x)}+\tg(x) \cdot \ln(x)+C</x:v>
+        <x:v>y=x^{2} \cdot \frac{1}{\arcctg(x)}+\arctg(x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
       <x:c r="C48" t="str">
         <x:v>separable variables</x:v>
@@ -935,10 +935,10 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
-        <x:v>y^{\prime}=\frac{x^{2}}{\left(x^{2} + 1\right) \operatorname{acot}^{2}{\left(x \right)}} + \frac{2 x}{\operatorname{acot}{\left(x \right)}} + \frac{1}{\left(x^{2} + 1\right) \operatorname{asin}{\left(x \right)}} - \frac{\operatorname{atan}{\left(x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=\frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 \operatorname{ctan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} + \frac{1}{x \sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{x^{2}}</x:v>
       </x:c>
       <x:c r="B49" t="str">
-        <x:v>y=x^{2} \cdot \frac{1}{\arcctg(x)}+\arctg(x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
+        <x:v>y=\ctg(x) \cdot \frac{1}{\arcsin(2 \cdot x)}-\arccos(x) \cdot \frac{1}{x}+C</x:v>
       </x:c>
       <x:c r="C49" t="str">
         <x:v>separable variables</x:v>
@@ -946,10 +946,10 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
-        <x:v>y^{\prime}=\frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 \operatorname{ctan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} + \frac{1}{x \sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{x^{2}}</x:v>
+        <x:v>y^{\prime}=- \frac{2 x^{2}}{\sqrt{1 - 4 x^{2}}} + 2 x \operatorname{acos}{\left(2 x \right)} + \frac{2 \sin{\left(2 x \right)}}{\operatorname{asin}{\left(x \right)}} + \frac{\cos{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>y=\ctg(x) \cdot \frac{1}{\arcsin(2 \cdot x)}-\arccos(x) \cdot \frac{1}{x}+C</x:v>
+        <x:v>y=x^{2} \cdot \arccos(2 \cdot x)-\cos(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
       <x:c r="C50" t="str">
         <x:v>separable variables</x:v>
@@ -957,10 +957,10 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
-        <x:v>y^{\prime}=- \frac{2 x^{2}}{\sqrt{1 - 4 x^{2}}} + 2 x \operatorname{acos}{\left(2 x \right)} + \frac{2 \sin{\left(2 x \right)}}{\operatorname{asin}{\left(x \right)}} + \frac{\cos{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \sin{\left(x \right)} + e^{x} \cos{\left(x \right)} + \frac{\sin{\left(x \right)}}{\operatorname{atan}{\left(2 x \right)}} + \frac{2 \cos{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>y=x^{2} \cdot \arccos(2 \cdot x)-\cos(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
+        <x:v>y=e^{x} \cdot \sin(x)-\cos(x) \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C51" t="str">
         <x:v>separable variables</x:v>
@@ -968,10 +968,10 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
-        <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \sin{\left(x \right)} + e^{x} \cos{\left(x \right)} + \frac{\sin{\left(x \right)}}{\operatorname{atan}{\left(2 x \right)}} + \frac{2 \cos{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=- \frac{x^{2}}{x^{2} + 1} + 2 x \operatorname{acot}{\left(x \right)} - \frac{2 \log{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} + \frac{\operatorname{acos}{\left(2 x \right)}}{x}</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>y=e^{x} \cdot \sin(x)-\cos(x) \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
+        <x:v>y=\ln(2 \cdot x) \cdot \arccos(2 \cdot x)+\arcctg(x) \cdot x^{2}+C</x:v>
       </x:c>
       <x:c r="C52" t="str">
         <x:v>separable variables</x:v>
@@ -979,10 +979,10 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
-        <x:v>y^{\prime}=- \frac{x^{2}}{x^{2} + 1} + 2 x \operatorname{acot}{\left(x \right)} - \frac{2 \log{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} + \frac{\operatorname{acos}{\left(2 x \right)}}{x}</x:v>
+        <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{ctan}{\left(x \right)} + \tan{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + \frac{1}{\left(x^{2} + 1\right) \log{\left(2 x \right)}} + \frac{\operatorname{acot}{\left(x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>y=\ln(2 \cdot x) \cdot \arccos(2 \cdot x)+\arcctg(x) \cdot x^{2}+C</x:v>
+        <x:v>y=\ctg(x) \cdot \tg(2 \cdot x)-\arcctg(x) \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
       <x:c r="C53" t="str">
         <x:v>separable variables</x:v>
@@ -990,10 +990,10 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
-        <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{ctan}{\left(x \right)} + \tan{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + \frac{1}{\left(x^{2} + 1\right) \log{\left(2 x \right)}} + \frac{\operatorname{acot}{\left(x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
+        <x:v>y^{\prime}=- \frac{3 \log{\left(2 x \right)}}{x^{4}} + \frac{1}{x^{4}}</x:v>
       </x:c>
       <x:c r="B54" t="str">
-        <x:v>y=\ctg(x) \cdot \tg(2 \cdot x)-\arcctg(x) \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
+        <x:v>y=\ln(2 \cdot x) \cdot \frac{1}{x^{3}}+\arctg(x) \cdot \sin(2 \cdot x)+C</x:v>
       </x:c>
       <x:c r="C54" t="str">
         <x:v>separable variables</x:v>
@@ -1001,10 +1001,10 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
-        <x:v>y^{\prime}=- \frac{3 \log{\left(2 x \right)}}{x^{4}} + \frac{1}{x^{4}}</x:v>
+        <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{asin}{\left(x \right)} + \frac{\log{\left(2 x \right)} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}} - \frac{1}{x \sin{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B55" t="str">
-        <x:v>y=\ln(2 \cdot x) \cdot \frac{1}{x^{3}}+\arctg(x) \cdot \sin(2 \cdot x)+C</x:v>
+        <x:v>y=\tg(x) \cdot \arcsin(x)-\ln(2 \cdot x) \cdot \frac{1}{\sin(x)}+C</x:v>
       </x:c>
       <x:c r="C55" t="str">
         <x:v>separable variables</x:v>
@@ -1012,10 +1012,10 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
-        <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{asin}{\left(x \right)} + \frac{\log{\left(2 x \right)} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}} - \frac{1}{x \sin{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=- \frac{2 \sin{\left(2 x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{\log{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{2 \cos{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} + \frac{1}{x \operatorname{ctan}{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B56" t="str">
-        <x:v>y=\tg(x) \cdot \arcsin(x)-\ln(2 \cdot x) \cdot \frac{1}{\sin(x)}+C</x:v>
+        <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+\ln(2 \cdot x) \cdot \frac{1}{\ctg(x)}+C</x:v>
       </x:c>
       <x:c r="C56" t="str">
         <x:v>separable variables</x:v>
@@ -1023,10 +1023,10 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
-        <x:v>y^{\prime}=- \frac{2 \sin{\left(2 x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{\log{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{2 \cos{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} + \frac{1}{x \operatorname{ctan}{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{acos}{\left(x \right)} - \log{\left(x \right)} - 1 - \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
       <x:c r="B57" t="str">
-        <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+\ln(2 \cdot x) \cdot \frac{1}{\ctg(x)}+C</x:v>
+        <x:v>y=\tg(x) \cdot \arccos(x)-\ln(x) \cdot x+C</x:v>
       </x:c>
       <x:c r="C57" t="str">
         <x:v>separable variables</x:v>
@@ -1034,10 +1034,10 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
-        <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{acos}{\left(x \right)} - \log{\left(x \right)} - 1 - \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
+        <x:v>y^{\prime}=\frac{2 \sin{\left(2 x \right)} \operatorname{acos}{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \cos{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B58" t="str">
-        <x:v>y=\tg(x) \cdot \arccos(x)-\ln(x) \cdot x+C</x:v>
+        <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\cos(2 \cdot x)}+\arcctg(2 \cdot x) \cdot x^{3}+C</x:v>
       </x:c>
       <x:c r="C58" t="str">
         <x:v>separable variables</x:v>
@@ -1045,10 +1045,10 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
-        <x:v>y^{\prime}=\frac{2 \sin{\left(2 x \right)} \operatorname{acos}{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \cos{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=\frac{2 x \sin{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} + \frac{1}{\cos{\left(2 x \right)}}</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\cos(2 \cdot x)}+\arcctg(2 \cdot x) \cdot x^{3}+C</x:v>
+        <x:v>y=x \cdot \frac{1}{\cos(2 \cdot x)}+\ln(2 \cdot x) \cdot e^{2 \cdot x}+C</x:v>
       </x:c>
       <x:c r="C59" t="str">
         <x:v>separable variables</x:v>
@@ -1056,10 +1056,10 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
-        <x:v>y^{\prime}=\frac{e^{x} \left(- 2 \tan^{2}{\left(2 x \right)} - 2\right)}{\tan^{2}{\left(2 x \right)}} + \frac{e^{x} \log{\left(e \right)}}{\tan{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=\frac{2 \sin{\left(2 x \right)}}{\log{\left(x \right)}} + \frac{\cos{\left(x \right)}}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \sin{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} + \frac{\cos{\left(2 x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>y=e^{x} \cdot \frac{1}{\tg(2 \cdot x)}-\tg(x) \cdot \arctg(2 \cdot x)+C</x:v>
+        <x:v>y=\sin(x) \cdot \frac{1}{\ctg(2 \cdot x)}-\cos(2 \cdot x) \cdot \frac{1}{\ln(x)}+C</x:v>
       </x:c>
       <x:c r="C60" t="str">
         <x:v>separable variables</x:v>
@@ -1067,10 +1067,10 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
-        <x:v>y^{\prime}=\frac{2 x \sin{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} + \frac{1}{\cos{\left(2 x \right)}}</x:v>
+        <x:v>y^{\prime}=- \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{atan}{\left(x \right)}} - \frac{2 \operatorname{acot}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}} + \frac{\operatorname{ctan}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}}</x:v>
       </x:c>
       <x:c r="B61" t="str">
-        <x:v>y=x \cdot \frac{1}{\cos(2 \cdot x)}+\ln(2 \cdot x) \cdot e^{2 \cdot x}+C</x:v>
+        <x:v>y=\arcctg(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}-\ctg(x) \cdot \frac{1}{\arctg(x)}+C</x:v>
       </x:c>
       <x:c r="C61" t="str">
         <x:v>separable variables</x:v>
@@ -1078,10 +1078,10 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
-        <x:v>y^{\prime}=\frac{2 \sin{\left(2 x \right)}}{\log{\left(x \right)}} + \frac{\cos{\left(x \right)}}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \sin{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} + \frac{\cos{\left(2 x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
+        <x:v>y^{\prime}=e^{x} x \log{\left(e \right)} + e^{x} + \left(2 \tan^{2}{\left(2 x \right)} + 2\right) \sin{\left(x \right)} + \cos{\left(x \right)} \tan{\left(2 x \right)}</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>y=\sin(x) \cdot \frac{1}{\ctg(2 \cdot x)}-\cos(2 \cdot x) \cdot \frac{1}{\ln(x)}+C</x:v>
+        <x:v>y=\tg(2 \cdot x) \cdot \sin(x)+e^{x} \cdot x+C</x:v>
       </x:c>
       <x:c r="C62" t="str">
         <x:v>separable variables</x:v>
@@ -1089,10 +1089,10 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
-        <x:v>y^{\prime}=- \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{atan}{\left(x \right)}} - \frac{2 \operatorname{acot}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}} + \frac{\operatorname{ctan}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}}</x:v>
+        <x:v>y^{\prime}=- \frac{2 \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{asin}{\left(x \right)}} - \frac{1}{\left(x^{2} + 1\right) \log{\left(2 x \right)}} + \frac{\operatorname{ctan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{\operatorname{acot}{\left(x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
       <x:c r="B63" t="str">
-        <x:v>y=\arcctg(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}-\ctg(x) \cdot \frac{1}{\arctg(x)}+C</x:v>
+        <x:v>y=\arcctg(x) \cdot \frac{1}{\ln(2 \cdot x)}-\ctg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
       <x:c r="C63" t="str">
         <x:v>separable variables</x:v>
@@ -1100,10 +1100,10 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>y^{\prime}=e^{x} x \log{\left(e \right)} + e^{x} + \left(2 \tan^{2}{\left(2 x \right)} + 2\right) \sin{\left(x \right)} + \cos{\left(x \right)} \tan{\left(2 x \right)}</x:v>
+        <x:v>y^{\prime}=- \frac{x}{x^{2} + 1} + 2 \log{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - \operatorname{atan}{\left(x \right)} + \frac{\operatorname{ctan}{\left(2 x \right)}}{x}</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>y=\tg(2 \cdot x) \cdot \sin(x)+e^{x} \cdot x+C</x:v>
+        <x:v>y=\ln(2 \cdot x) \cdot \ctg(2 \cdot x)-\arctg(x) \cdot x+C</x:v>
       </x:c>
       <x:c r="C64" t="str">
         <x:v>separable variables</x:v>
@@ -1111,36 +1111,24 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
-        <x:v>y^{\prime}=- \frac{2 \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{asin}{\left(x \right)}} - \frac{1}{\left(x^{2} + 1\right) \log{\left(2 x \right)}} + \frac{\operatorname{ctan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{\operatorname{acot}{\left(x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
+        <x:v>y^{\prime}=- \frac{2 e^{2 x} \log{\left(e \right)}}{\cos{\left(x \right)}} - \frac{e^{2 x} \sin{\left(x \right)}}{\cos^{2}{\left(x \right)}} + \left(\tan^{2}{\left(x \right)} + 1\right) \log{\left(x \right)} + \frac{\tan{\left(x \right)}}{x}</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>y=\arcctg(x) \cdot \frac{1}{\ln(2 \cdot x)}-\ctg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
+        <x:v>y=\tg(x) \cdot \ln(x)-e^{2 \cdot x} \cdot \frac{1}{\cos(x)}+C</x:v>
       </x:c>
       <x:c r="C65" t="str">
         <x:v>separable variables</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" t="str">
-        <x:v>y^{\prime}=- \frac{x}{x^{2} + 1} + 2 \log{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - \operatorname{atan}{\left(x \right)} + \frac{\operatorname{ctan}{\left(2 x \right)}}{x}</x:v>
-      </x:c>
-      <x:c r="B66" t="str">
-        <x:v>y=\ln(2 \cdot x) \cdot \ctg(2 \cdot x)-\arctg(x) \cdot x+C</x:v>
-      </x:c>
-      <x:c r="C66" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
+      <x:c r="A66"/>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" t="str">
-        <x:v>y^{\prime}=- \frac{2 e^{2 x} \log{\left(e \right)}}{\cos{\left(x \right)}} - \frac{e^{2 x} \sin{\left(x \right)}}{\cos^{2}{\left(x \right)}} + \left(\tan^{2}{\left(x \right)} + 1\right) \log{\left(x \right)} + \frac{\tan{\left(x \right)}}{x}</x:v>
-      </x:c>
-      <x:c r="B67" t="str">
-        <x:v>y=\tg(x) \cdot \ln(x)-e^{2 \cdot x} \cdot \frac{1}{\cos(x)}+C</x:v>
-      </x:c>
-      <x:c r="C67" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
+      <x:c r="A67"/>
+      <x:c r="B67"/>
+      <x:c r="C67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68"/>
